--- a/output/graficos_regionales_indicadores/plot_regional_o_ocup_a_2018_aysen.xlsx
+++ b/output/graficos_regionales_indicadores/plot_regional_o_ocup_a_2018_aysen.xlsx
@@ -85,7 +85,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 18:12</t>
+    <t xml:space="preserve">2026-09-09 19:00</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_indicadores/plot_regional_o_ocup_a_2018_aysen.xlsx
+++ b/output/graficos_regionales_indicadores/plot_regional_o_ocup_a_2018_aysen.xlsx
@@ -85,7 +85,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 19:00</t>
+    <t xml:space="preserve">2026-09-18 09:08</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_indicadores/plot_regional_o_ocup_a_2018_aysen.xlsx
+++ b/output/graficos_regionales_indicadores/plot_regional_o_ocup_a_2018_aysen.xlsx
@@ -85,7 +85,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 09:08</t>
+    <t xml:space="preserve">2026-10-05 06:47</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
